--- a/assets/docs/02_Task_Management_Dashboard.xlsx
+++ b/assets/docs/02_Task_Management_Dashboard.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Task Tracker'!$A$1:$G$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Task Tracker'!$A$1:$I$8</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -30,10 +30,15 @@
     </font>
     <font>
       <b val="1"/>
+      <color rgb="00FFFFFF"/>
     </font>
     <font>
       <b val="1"/>
+      <color rgb="00FFFFFF"/>
       <sz val="16"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -45,7 +50,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D9EAF7"/>
+        <fgColor rgb="001F1A12"/>
       </patternFill>
     </fill>
   </fills>
@@ -61,11 +66,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -431,247 +442,378 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="35" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>Task ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
           <t>Task</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Client</t>
-        </is>
-      </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Assigned To</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>Priority</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Assigned To</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Due Date</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Date Completed</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Organize client files</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>ABC Corp</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>T-001</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Update client database</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Data Management</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>Verified records</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>T-002</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Prepare weekly report</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Reporting</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>VA</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr"/>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>Waiting for final update</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>T-003</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Organize Google Drive</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>File Management</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr"/>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>Folder naming review</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>T-004</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Send invoice follow-up</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr"/>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>Draft prepared</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>T-005</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Confirm client meeting</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Calendar</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>2026-08-13</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>Invite accepted</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>T-006</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Create onboarding checklist</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Documentation</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>In Progress</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Digital files</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Update database</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>XYZ Ltd</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr"/>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>Draft version 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>T-007</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Archive completed files</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>File Management</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>VA</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>25 records</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Schedule meeting</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>ABC Corp</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>VA</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Zoom</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Prepare weekly report</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>XYZ Ltd</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>VA</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>2026-08-15</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Friday report</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Follow up on invoice</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>ABC Corp</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>VA</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Awaiting confirmation</t>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr"/>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>Archive after approval</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G6"/>
-  <dataValidations count="1">
-    <dataValidation sqref="F2:F1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Not Started,In Progress,Completed,On Hold"</formula1>
-    </dataValidation>
-  </dataValidations>
+  <autoFilter ref="A1:I8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -682,98 +824,79 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="25" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>WEEKLY ADMINISTRATIVE TASK DASHBOARD</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>ADMINISTRATIVE TASK DASHBOARD</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>Total Tasks</t>
         </is>
       </c>
-      <c r="B3">
+      <c r="B2" s="4">
         <f>COUNTA('Task Tracker'!A2:A)</f>
         <v/>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="B3" s="4">
+        <f>COUNTIF('Task Tracker'!G2:G,"Completed")</f>
+        <v/>
+      </c>
+    </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="B4">
-        <f>COUNTIF('Task Tracker'!F2:F,"Completed")</f>
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="B4" s="4">
+        <f>COUNTIF('Task Tracker'!G2:G,"In Progress")</f>
         <v/>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>In Progress</t>
-        </is>
-      </c>
-      <c r="B5">
-        <f>COUNTIF('Task Tracker'!F2:F,"In Progress")</f>
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="B5" s="4">
+        <f>COUNTIF('Task Tracker'!G2:G,"Pending")</f>
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="B6">
-        <f>COUNTIF('Task Tracker'!F2:F,"Not Started")</f>
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Completion Rate</t>
+        </is>
+      </c>
+      <c r="B6" s="5">
+        <f>IFERROR(B3/B2,0)</f>
         <v/>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>On Hold</t>
-        </is>
-      </c>
-      <c r="B7">
-        <f>COUNTIF('Task Tracker'!F2:F,"On Hold")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Completion Rate</t>
-        </is>
-      </c>
-      <c r="B8" s="3">
-        <f>IFERROR(COUNTIF('Task Tracker'!F2:F,"Completed")/COUNTA('Task Tracker'!A2:A),0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Overdue</t>
-        </is>
-      </c>
-      <c r="B9">
-        <f>COUNTIFS('Task Tracker'!E2:E,"&lt;"&amp;TODAY(),'Task Tracker'!F2:F,"&lt;&gt;Completed",'Task Tracker'!A2:A,"&lt;&gt;")</f>
-        <v/>
-      </c>
-    </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:D1"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>